--- a/data/raw/bank_c_statement_2026Q1.xlsx
+++ b/data/raw/bank_c_statement_2026Q1.xlsx
@@ -1819,7 +1819,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2027-02-25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
